--- a/ClosedXML.Tests/Resource/Examples/Ranges/TransposeRanges.xlsx
+++ b/ClosedXML.Tests/Resource/Examples/Ranges/TransposeRanges.xlsx
@@ -103,23 +103,23 @@
     <border>
       <left/>
       <right style="thick">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </right>
       <top/>
       <bottom style="thick">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thick">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </right>
       <top style="thick">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -127,10 +127,10 @@
     <border>
       <left/>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </right>
       <top style="thick">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -138,20 +138,20 @@
     <border>
       <left/>
       <right style="thick">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </right>
       <top style="thick">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thick">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </right>
       <top/>
       <bottom/>
@@ -160,7 +160,7 @@
     <border>
       <left/>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </right>
       <top/>
       <bottom/>
@@ -169,7 +169,7 @@
     <border>
       <left/>
       <right style="thick">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </right>
       <top/>
       <bottom/>
@@ -177,25 +177,25 @@
     </border>
     <border>
       <left style="thick">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </right>
       <top/>
       <bottom style="thick">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </right>
       <top/>
       <bottom style="thick">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
